--- a/設計書/個別画面設計書.xlsx
+++ b/設計書/個別画面設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\職業判断\設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A19644AC-1C2F-4110-994B-79B35EDBE04F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48882B2E-CDBC-4199-998B-89DC3D01EF0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="6" activeTab="11" xr2:uid="{ACE3C624-1D29-493B-96CA-4E4A907CF828}"/>
+    <workbookView xWindow="240" yWindow="0" windowWidth="10720" windowHeight="13650" firstSheet="5" activeTab="6" xr2:uid="{ACE3C624-1D29-493B-96CA-4E4A907CF828}"/>
   </bookViews>
   <sheets>
     <sheet name="ログイン画面" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="価値観診断結果" sheetId="11" r:id="rId9"/>
     <sheet name="適性診断" sheetId="13" r:id="rId10"/>
     <sheet name="適性診断結果 " sheetId="14" r:id="rId11"/>
-    <sheet name="DISC診断 (2)" sheetId="18" r:id="rId12"/>
+    <sheet name="診断履歴" sheetId="18" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="263">
   <si>
     <t>個別画面設計書</t>
     <rPh sb="0" eb="2">
@@ -2241,6 +2241,55 @@
     <rPh sb="5" eb="6">
       <t>ダ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>11.1ページ概要</t>
+    <rPh sb="7" eb="9">
+      <t>ガイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>11.2 画面レイアウト</t>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>11.3 画面項目定義</t>
+    <rPh sb="5" eb="11">
+      <t>ガメンコウモクテイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>11.4　入出力一覧</t>
+    <rPh sb="5" eb="8">
+      <t>ニュウシュツリョク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>11.5　画面イベント一覧</t>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>11.7　DBアクセス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ログアウト完了後、ユーザに完了を通知しログイン画面へ遷移させる </t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2407,7 +2456,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2446,12 +2495,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2787,8 +2830,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1320800" y="2057400"/>
-          <a:ext cx="10202699" cy="9935962"/>
+          <a:off x="1270000" y="2286000"/>
+          <a:ext cx="10183649" cy="11028162"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4778,7 +4821,7 @@
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.55000000000000004">
@@ -4807,12 +4850,12 @@
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.55000000000000004">
@@ -4995,7 +5038,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E281DF8-23DD-4FFC-B272-C7E31AE4A0CC}">
-  <dimension ref="B2:AV84"/>
+  <dimension ref="B2:L84"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="3" max="3" width="10.4140625" bestFit="1" customWidth="1"/>
@@ -5010,7 +5053,7 @@
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" t="s">
-        <v>192</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.55000000000000004">
@@ -5039,12 +5082,12 @@
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" t="s">
-        <v>178</v>
+        <v>257</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" t="s">
-        <v>179</v>
+        <v>258</v>
       </c>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.55000000000000004">
@@ -5214,7 +5257,7 @@
     </row>
     <row r="53" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" t="s">
-        <v>180</v>
+        <v>259</v>
       </c>
     </row>
     <row r="55" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -5381,7 +5424,7 @@
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" t="s">
-        <v>181</v>
+        <v>260</v>
       </c>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.55000000000000004">
@@ -5496,12 +5539,12 @@
       <c r="H78" s="6"/>
       <c r="I78" s="6"/>
     </row>
-    <row r="81" spans="2:48" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B81" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="83" spans="2:48" x14ac:dyDescent="0.55000000000000004">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="83" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="C83" s="6" t="s">
         <v>23</v>
       </c>
@@ -5514,50 +5557,9 @@
       <c r="F83" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="G83" s="14"/>
-      <c r="H83" s="13"/>
-      <c r="I83" s="13"/>
-      <c r="J83" s="13"/>
-      <c r="K83" s="13"/>
-      <c r="L83" s="13"/>
-      <c r="M83" s="13"/>
-      <c r="N83" s="13"/>
-      <c r="O83" s="13"/>
-      <c r="P83" s="13"/>
-      <c r="Q83" s="13"/>
-      <c r="R83" s="13"/>
-      <c r="S83" s="13"/>
-      <c r="T83" s="13"/>
-      <c r="U83" s="13"/>
-      <c r="V83" s="13"/>
-      <c r="W83" s="13"/>
-      <c r="X83" s="13"/>
-      <c r="Y83" s="13"/>
-      <c r="Z83" s="13"/>
-      <c r="AA83" s="13"/>
-      <c r="AB83" s="13"/>
-      <c r="AC83" s="13"/>
-      <c r="AD83" s="13"/>
-      <c r="AE83" s="13"/>
-      <c r="AF83" s="13"/>
-      <c r="AG83" s="13"/>
-      <c r="AH83" s="13"/>
-      <c r="AI83" s="13"/>
-      <c r="AJ83" s="13"/>
-      <c r="AK83" s="13"/>
-      <c r="AL83" s="13"/>
-      <c r="AM83" s="13"/>
-      <c r="AN83" s="13"/>
-      <c r="AO83" s="13"/>
-      <c r="AP83" s="13"/>
-      <c r="AQ83" s="13"/>
-      <c r="AR83" s="13"/>
-      <c r="AS83" s="13"/>
-      <c r="AT83" s="13"/>
-      <c r="AU83" s="13"/>
-      <c r="AV83" s="13"/>
-    </row>
-    <row r="84" spans="2:48" x14ac:dyDescent="0.55000000000000004">
+      <c r="G83" s="11"/>
+    </row>
+    <row r="84" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="C84" s="6">
         <v>1</v>
       </c>
@@ -5570,48 +5572,6 @@
       <c r="F84" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="G84" s="13"/>
-      <c r="H84" s="13"/>
-      <c r="I84" s="13"/>
-      <c r="J84" s="13"/>
-      <c r="K84" s="13"/>
-      <c r="L84" s="13"/>
-      <c r="M84" s="13"/>
-      <c r="N84" s="13"/>
-      <c r="O84" s="13"/>
-      <c r="P84" s="13"/>
-      <c r="Q84" s="13"/>
-      <c r="R84" s="13"/>
-      <c r="S84" s="13"/>
-      <c r="T84" s="13"/>
-      <c r="U84" s="13"/>
-      <c r="V84" s="13"/>
-      <c r="W84" s="13"/>
-      <c r="X84" s="13"/>
-      <c r="Y84" s="13"/>
-      <c r="Z84" s="13"/>
-      <c r="AA84" s="13"/>
-      <c r="AB84" s="13"/>
-      <c r="AC84" s="13"/>
-      <c r="AD84" s="13"/>
-      <c r="AE84" s="13"/>
-      <c r="AF84" s="13"/>
-      <c r="AG84" s="13"/>
-      <c r="AH84" s="13"/>
-      <c r="AI84" s="13"/>
-      <c r="AJ84" s="13"/>
-      <c r="AK84" s="13"/>
-      <c r="AL84" s="13"/>
-      <c r="AM84" s="13"/>
-      <c r="AN84" s="13"/>
-      <c r="AO84" s="13"/>
-      <c r="AP84" s="13"/>
-      <c r="AQ84" s="13"/>
-      <c r="AR84" s="13"/>
-      <c r="AS84" s="13"/>
-      <c r="AT84" s="13"/>
-      <c r="AU84" s="13"/>
-      <c r="AV84" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -5658,7 +5618,7 @@
         <v>204</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>2</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.55000000000000004">
